--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580880</v>
+        <v>123580093</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -725,13 +735,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539211</v>
+        <v>539222</v>
       </c>
       <c r="R2" t="n">
-        <v>6436801</v>
+        <v>6436675</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +770,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +780,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,23 +794,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580093</v>
+        <v>123580939</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,7 +848,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +858,9 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539222</v>
+        <v>539227</v>
       </c>
       <c r="R3" t="n">
-        <v>6436675</v>
+        <v>6436728</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -931,7 +931,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -950,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580939</v>
+        <v>123580880</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>8445</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,40 +961,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539227</v>
+        <v>539211</v>
       </c>
       <c r="R4" t="n">
-        <v>6436728</v>
+        <v>6436801</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,6 +1055,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1086,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123579996</v>
+        <v>123581028</v>
       </c>
       <c r="B5" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,56 +1098,60 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539176</v>
+        <v>539308</v>
       </c>
       <c r="R5" t="n">
-        <v>6436662</v>
+        <v>6436591</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,7 +1190,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1200,24 +1204,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1227,17 +1215,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123581028</v>
+        <v>123579996</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>91003</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1246,60 +1234,56 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539308</v>
+        <v>539176</v>
       </c>
       <c r="R6" t="n">
-        <v>6436591</v>
+        <v>6436662</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1328,7 +1312,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,7 +1322,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1352,8 +1336,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
         <v>123579966</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580093</v>
+        <v>123580880</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>8447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -735,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539222</v>
+        <v>539211</v>
       </c>
       <c r="R2" t="n">
-        <v>6436675</v>
+        <v>6436801</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,12 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,9 +779,23 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -813,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580939</v>
+        <v>123580093</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -848,7 +847,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,9 +857,10 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539227</v>
+        <v>539222</v>
       </c>
       <c r="R3" t="n">
-        <v>6436728</v>
+        <v>6436675</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -931,6 +931,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -949,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580880</v>
+        <v>123580939</v>
       </c>
       <c r="B4" t="n">
-        <v>8445</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,31 +962,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +1009,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539211</v>
+        <v>539227</v>
       </c>
       <c r="R4" t="n">
-        <v>6436801</v>
+        <v>6436728</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1054,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,21 +1070,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1086,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123581028</v>
+        <v>123579966</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539308</v>
+        <v>539176</v>
       </c>
       <c r="R5" t="n">
-        <v>6436591</v>
+        <v>6436662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123579996</v>
+        <v>123581028</v>
       </c>
       <c r="B6" t="n">
-        <v>91003</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1234,56 +1234,60 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539176</v>
+        <v>539308</v>
       </c>
       <c r="R6" t="n">
-        <v>6436662</v>
+        <v>6436591</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1312,7 +1316,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1322,7 +1326,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1336,24 +1340,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1363,17 +1351,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123579966</v>
+        <v>123579996</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,47 +1370,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
@@ -1488,8 +1472,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580880</v>
+        <v>123580093</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -725,13 +735,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539211</v>
+        <v>539222</v>
       </c>
       <c r="R2" t="n">
-        <v>6436801</v>
+        <v>6436675</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +770,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +780,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,23 +794,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580093</v>
+        <v>123580939</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,7 +848,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +858,9 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539222</v>
+        <v>539227</v>
       </c>
       <c r="R3" t="n">
-        <v>6436675</v>
+        <v>6436728</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -931,7 +931,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -950,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580939</v>
+        <v>123580880</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,40 +961,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539227</v>
+        <v>539211</v>
       </c>
       <c r="R4" t="n">
-        <v>6436728</v>
+        <v>6436801</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,6 +1055,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1089,7 +1089,7 @@
         <v>123579966</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>123581028</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>123579996</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580093</v>
+        <v>123580939</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,10 +720,9 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -735,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539222</v>
+        <v>539227</v>
       </c>
       <c r="R2" t="n">
-        <v>6436675</v>
+        <v>6436728</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -770,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -794,7 +793,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -813,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580939</v>
+        <v>123580880</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,40 +823,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -872,13 +861,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539227</v>
+        <v>539211</v>
       </c>
       <c r="R3" t="n">
-        <v>6436728</v>
+        <v>6436801</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,12 +906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,6 +917,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -949,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580880</v>
+        <v>123580093</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,33 +960,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -999,13 +1008,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539211</v>
+        <v>539222</v>
       </c>
       <c r="R4" t="n">
-        <v>6436801</v>
+        <v>6436675</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,23 +1067,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1086,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123579966</v>
+        <v>123579996</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,47 +1098,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
@@ -1204,8 +1200,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1222,10 +1234,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123581028</v>
+        <v>123579966</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,7 +1269,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1267,7 +1279,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1281,13 +1293,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539308</v>
+        <v>539176</v>
       </c>
       <c r="R6" t="n">
-        <v>6436591</v>
+        <v>6436662</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,7 +1328,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1326,7 +1338,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,17 +1363,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123579996</v>
+        <v>123581028</v>
       </c>
       <c r="B7" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,56 +1382,60 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539176</v>
+        <v>539308</v>
       </c>
       <c r="R7" t="n">
-        <v>6436662</v>
+        <v>6436591</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1448,7 +1464,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1458,7 +1474,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1472,24 +1488,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580939</v>
+        <v>123580093</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,9 +720,10 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -734,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539227</v>
+        <v>539222</v>
       </c>
       <c r="R2" t="n">
-        <v>6436728</v>
+        <v>6436675</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -769,7 +770,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +780,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -793,6 +794,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -948,7 +950,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580093</v>
+        <v>123580939</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -983,7 +985,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -993,10 +995,9 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1008,10 +1009,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539222</v>
+        <v>539227</v>
       </c>
       <c r="R4" t="n">
-        <v>6436675</v>
+        <v>6436728</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1043,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,7 +1054,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1067,7 +1068,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123579996</v>
+        <v>123581028</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,56 +1098,60 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539176</v>
+        <v>539308</v>
       </c>
       <c r="R5" t="n">
-        <v>6436662</v>
+        <v>6436591</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,7 +1190,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1200,24 +1204,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1227,7 +1215,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1370,10 +1358,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123581028</v>
+        <v>123579996</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,60 +1370,56 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539308</v>
+        <v>539176</v>
       </c>
       <c r="R7" t="n">
-        <v>6436591</v>
+        <v>6436662</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1464,7 +1448,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1474,7 +1458,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1488,8 +1472,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580880</v>
+        <v>123580939</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,31 +825,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -863,13 +872,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539211</v>
+        <v>539227</v>
       </c>
       <c r="R3" t="n">
-        <v>6436801</v>
+        <v>6436728</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,7 +917,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,21 +933,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -950,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580939</v>
+        <v>123580880</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,40 +961,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539227</v>
+        <v>539211</v>
       </c>
       <c r="R4" t="n">
-        <v>6436728</v>
+        <v>6436801</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,6 +1055,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1086,7 +1086,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123581028</v>
+        <v>123579966</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539308</v>
+        <v>539176</v>
       </c>
       <c r="R5" t="n">
-        <v>6436591</v>
+        <v>6436662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1215,14 +1215,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123579966</v>
+        <v>123581028</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539176</v>
+        <v>539308</v>
       </c>
       <c r="R6" t="n">
-        <v>6436662</v>
+        <v>6436591</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580093</v>
+        <v>123580939</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,10 +720,9 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -735,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539222</v>
+        <v>539227</v>
       </c>
       <c r="R2" t="n">
-        <v>6436675</v>
+        <v>6436728</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -770,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -794,7 +793,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -813,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580939</v>
+        <v>123580093</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -848,7 +846,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,9 +856,10 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -872,10 +871,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539227</v>
+        <v>539222</v>
       </c>
       <c r="R3" t="n">
-        <v>6436728</v>
+        <v>6436675</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -907,7 +906,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,7 +916,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -931,6 +930,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123579966</v>
+        <v>123581028</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539176</v>
+        <v>539308</v>
       </c>
       <c r="R5" t="n">
-        <v>6436662</v>
+        <v>6436591</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1215,14 +1215,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123581028</v>
+        <v>123579966</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539308</v>
+        <v>539176</v>
       </c>
       <c r="R6" t="n">
-        <v>6436591</v>
+        <v>6436662</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123581028</v>
+        <v>123579966</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539308</v>
+        <v>539176</v>
       </c>
       <c r="R5" t="n">
-        <v>6436591</v>
+        <v>6436662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1215,14 +1215,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123579966</v>
+        <v>123581028</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539176</v>
+        <v>539308</v>
       </c>
       <c r="R6" t="n">
-        <v>6436662</v>
+        <v>6436591</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,134 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129866902</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mårdbergets barrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>539219</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6436696</v>
+      </c>
+      <c r="S8" t="n">
+        <v>46</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>E-Kin-0759</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sammanslagning av 3 lokaler. Avverkningsanmält: A 11477-2025</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11477-2025 artfynd.xlsx
+++ b/artfynd/A 11477-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
